--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{DFCCF669-693F-472A-9B24-8CCA25BAEC78}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{790B258F-0D19-4C81-BE58-6EE2D5BF2DBF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="7" windowHeight="15840" windowWidth="29040" xWindow="28680" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-3945"/>
+    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="2952"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" r:id="rId1" sheetId="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="288">
   <si>
     <t>Result</t>
   </si>
@@ -204,303 +204,21 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:07:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:08:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:08:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:08:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:08:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:09:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:09:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:09:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:10:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:10:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:10:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:11:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:11:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:11:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:12:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:12:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:13:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:13:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:13:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:14:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:14:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:14:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:15:02 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:15:20 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:15:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:16:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:16:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:16:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:17:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:17:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:17:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:17:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:18:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:18:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:18:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:19:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:19:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:19:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:20:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:20:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:20:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:21:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:21:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:21:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:22:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:22:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:22:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:23:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:23:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:24:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:24:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:24:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:25:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:25:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:26:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:26:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:26:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:27:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:27:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:27:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:28:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:28:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:28:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:29:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:29:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:30:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:30:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:30:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:31:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:31:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:31:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:32:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:32:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:32:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:33:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:33:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:33:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:34:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:34:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:34:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:35:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:35:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:35:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:36:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:36:40 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:37:00 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:37:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:37:41 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:38:02 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:38:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:38:47 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:39:07 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:39:29 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:39:49 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:40:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:40:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:40:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:41:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:41:46 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:42:09 EST 2025</t>
   </si>
   <si>
@@ -510,19 +228,307 @@
     <t>Mon Feb 24 23:42:58 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:43:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:44:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:44:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:45:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:45:57 EST 2025</t>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:57:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:57:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:58:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 20:59:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:00:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:01:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:02:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:03:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:04:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:05:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:06:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:07:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:08:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:09:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:09:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:09:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:09:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:09:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:10:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue May 12 21:10:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>June</t>
   </si>
   <si>
     <t/>
@@ -531,613 +537,376 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Sat Oct 04 13:28:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:28:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:29:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:30:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:31:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:32:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:33:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:34:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:49 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 13:35:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:55:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:55:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:56:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:56:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:56:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:26:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:26:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:26:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:26:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:26:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:27:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:28:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:29:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:30:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:31:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:32:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:33:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:34:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:35:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:36:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 04 21:37:14 EST 2025</t>
+    <t>Thu May 21 21:37:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:41:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:42:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:42:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:42:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:51:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:02:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:09:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:09:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:24:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:25:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:27:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:28:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:28:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:28:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:28:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:30:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:30:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:31:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:32:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:33:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:33:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:33:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:33:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:36:05 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1514,21 +1283,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.7265625" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.54296875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.54296875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.54296875" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,12 +1323,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1571,18 +1340,18 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1594,18 +1363,18 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1617,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1626,12 +1395,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1643,7 +1412,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1652,12 +1421,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1669,7 +1438,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1678,12 +1447,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1695,13 +1464,36 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1717,19 +1509,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.453125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.453125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
     <col min="8" max="8" customWidth="true" style="1" width="13.0" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1755,12 +1547,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1772,12 +1564,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1789,12 +1581,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1806,12 +1598,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1826,12 +1618,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1846,12 +1638,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1866,12 +1658,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>177</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1886,12 +1678,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>279</v>
+        <v>178</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1906,12 +1698,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1926,12 +1718,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>180</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1946,12 +1738,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>181</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1966,12 +1758,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1986,12 +1778,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>284</v>
+        <v>183</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2006,12 +1798,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>184</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2023,12 +1815,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>185</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2046,12 +1838,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>186</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2066,12 +1858,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>288</v>
+        <v>187</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2083,12 +1875,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>36</v>
@@ -2100,12 +1892,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>188</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2117,12 +1909,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>290</v>
+        <v>189</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2148,20 +1940,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.453125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
     <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2187,12 +1979,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>190</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2204,18 +1996,18 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>292</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2227,15 +2019,15 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2247,18 +2039,18 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>193</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2270,18 +2062,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>295</v>
+        <v>194</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2293,18 +2085,18 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>195</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2316,7 +2108,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>32</v>
@@ -2334,21 +2126,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
   <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.36328125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="39.54296875" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="14.453125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="12.7265625" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.33203125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="39.53125" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2377,12 +2169,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>208</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2394,15 +2186,15 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2414,18 +2206,18 @@
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2437,18 +2229,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2460,18 +2252,18 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2483,18 +2275,18 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2506,15 +2298,15 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>214</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2526,18 +2318,18 @@
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>215</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2549,18 +2341,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2572,18 +2364,18 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2595,18 +2387,18 @@
         <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2618,15 +2410,15 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>219</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2638,18 +2430,18 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2661,18 +2453,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2684,18 +2476,18 @@
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2707,18 +2499,18 @@
         <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>223</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2730,18 +2522,18 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2753,18 +2545,18 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>225</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2776,15 +2568,15 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>315</v>
+        <v>226</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2796,15 +2588,15 @@
         <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2816,18 +2608,18 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2839,18 +2631,18 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>318</v>
+        <v>229</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2862,15 +2654,15 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>319</v>
+        <v>230</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2882,18 +2674,18 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>320</v>
+        <v>231</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2905,7 +2697,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2914,12 +2706,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>321</v>
+        <v>232</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2931,18 +2723,18 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>322</v>
+        <v>233</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2954,15 +2746,15 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>323</v>
+        <v>234</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2974,18 +2766,18 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>324</v>
+        <v>235</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2997,18 +2789,18 @@
         <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>325</v>
+        <v>236</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -3020,18 +2812,18 @@
         <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>326</v>
+        <v>237</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -3043,15 +2835,15 @@
         <v>25</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>327</v>
+        <v>238</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -3063,15 +2855,15 @@
         <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -3083,18 +2875,18 @@
         <v>40</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>329</v>
+        <v>240</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -3106,18 +2898,18 @@
         <v>46</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -3129,15 +2921,15 @@
         <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -3149,18 +2941,18 @@
         <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -3172,7 +2964,7 @@
         <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>32</v>
@@ -3181,12 +2973,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -3204,12 +2996,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>334</v>
+        <v>245</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3221,15 +3013,15 @@
         <v>44</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3241,18 +3033,18 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3264,18 +3056,18 @@
         <v>38</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3287,18 +3079,18 @@
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>338</v>
+        <v>249</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3310,15 +3102,15 @@
         <v>25</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3330,15 +3122,15 @@
         <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3350,18 +3142,18 @@
         <v>40</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>341</v>
+        <v>252</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3373,18 +3165,18 @@
         <v>46</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>342</v>
+        <v>253</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3396,15 +3188,15 @@
         <v>41</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>343</v>
+        <v>254</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3416,18 +3208,18 @@
         <v>27</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>344</v>
+        <v>255</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3439,7 +3231,7 @@
         <v>42</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>32</v>
@@ -3448,12 +3240,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>345</v>
+        <v>256</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3465,18 +3257,18 @@
         <v>43</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>346</v>
+        <v>257</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3488,15 +3280,15 @@
         <v>44</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3508,18 +3300,18 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>348</v>
+        <v>259</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3531,15 +3323,15 @@
         <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>349</v>
+        <v>260</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -3551,18 +3343,18 @@
         <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>36</v>
@@ -3574,18 +3366,18 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3597,15 +3389,15 @@
         <v>51</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>351</v>
+        <v>262</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -3617,18 +3409,18 @@
         <v>52</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>36</v>
@@ -3640,18 +3432,18 @@
         <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>35</v>
       </c>
       <c r="B59" t="s">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3663,15 +3455,15 @@
         <v>51</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>35</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -3683,18 +3475,18 @@
         <v>52</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>35</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>36</v>
@@ -3706,7 +3498,7 @@
         <v>45</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>32</v>
@@ -3723,17 +3515,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3753,7 +3545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3764,7 +3556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
@@ -3772,7 +3564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3786,7 +3578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
@@ -3797,7 +3589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3808,7 +3600,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3830,17 +3622,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.81640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3860,12 +3652,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3877,15 +3669,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3897,15 +3689,15 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3917,15 +3709,15 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3937,15 +3729,15 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3957,15 +3749,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>36</v>
@@ -3980,12 +3772,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
@@ -4000,12 +3792,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>36</v>
@@ -4028,17 +3820,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.81640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4058,12 +3850,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>360</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4075,15 +3867,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>361</v>
+        <v>284</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4095,15 +3887,15 @@
         <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -4115,15 +3907,15 @@
         <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>286</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -4135,15 +3927,15 @@
         <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>287</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4155,7 +3947,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4166,17 +3958,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.81640625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4193,12 +3985,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4210,12 +4002,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>36</v>

--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{790B258F-0D19-4C81-BE58-6EE2D5BF2DBF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C787E33F-805E-4CF6-80B4-CB20221C641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="2952"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="7" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
-    <sheet name="Existing" r:id="rId2" sheetId="2"/>
-    <sheet name="Extension" r:id="rId3" sheetId="3"/>
-    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal" r:id="rId5" sheetId="5"/>
-    <sheet name="Personal_IND" r:id="rId6" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId7" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId8" sheetId="8"/>
+    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
+    <sheet name="Existing" sheetId="2" r:id="rId2"/>
+    <sheet name="Extension" sheetId="3" r:id="rId3"/>
+    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
+    <sheet name="Personal" sheetId="5" r:id="rId5"/>
+    <sheet name="Personal_IND" sheetId="6" r:id="rId6"/>
+    <sheet name="Personal_JNT" sheetId="7" r:id="rId7"/>
+    <sheet name="Personal_EL" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="260">
   <si>
     <t>Result</t>
   </si>
@@ -204,18 +204,6 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:15:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:37:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:38:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:39:07 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:39:49 EST 2025</t>
   </si>
   <si>
@@ -231,682 +219,610 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Tue May 12 20:57:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:57:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:58:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 20:59:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:00:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:01:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:02:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:03:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:04:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:05:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:06:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:07:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:08:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:09:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:09:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:09:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:09:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:09:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:10:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Tue May 12 21:10:26 EDT 2026</t>
-  </si>
-  <si>
     <t>June</t>
   </si>
   <si>
-    <t/>
+    <t>Thu May 21 21:37:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:37:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:38:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:39:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 21:40:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:02:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:03:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:05:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:06:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:07:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:08:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:09:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:25:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:29:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:30:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:30:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:35:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 19:36:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:34:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:34:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:34:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:35:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:35:15 EDT 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu May 21 21:37:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:41:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:42:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:42:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:42:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:51:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:02:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:09:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:09:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:24:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:25:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:27:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:28:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:28:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:28:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:28:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:30:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:30:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:31:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:32:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:33:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:33:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:33:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:33:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:36:05 EDT 2026</t>
+    <t>Thu Jul 09 22:10:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:10:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:10:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:11:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:12:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:13:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:14:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:15:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:16:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:17:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:18:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:19:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:20:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:21:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:21:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:21:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:21:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:21:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:22:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:22:15 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -962,19 +878,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -991,10 +907,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1029,7 +945,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1081,7 +997,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1192,21 +1108,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1223,7 +1139,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1275,15 +1191,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -1324,11 +1240,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>164</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1340,18 +1256,18 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>165</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1363,18 +1279,18 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>166</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1386,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1396,11 +1312,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>167</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1412,7 +1328,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1422,11 +1338,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>168</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1438,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1448,11 +1364,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>169</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1464,7 +1380,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1474,11 +1390,11 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>170</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1490,16 +1406,16 @@
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1507,8 +1423,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:I21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
@@ -1548,11 +1464,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>171</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1565,11 +1481,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>172</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1582,11 +1498,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>173</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1599,11 +1515,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>174</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1619,11 +1535,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>175</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1639,11 +1555,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>176</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1659,11 +1575,11 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>177</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1679,11 +1595,11 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>178</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1699,11 +1615,11 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>179</v>
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1719,11 +1635,11 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>180</v>
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1739,11 +1655,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>181</v>
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1759,11 +1675,11 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>182</v>
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1779,11 +1695,11 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>183</v>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1799,11 +1715,11 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>184</v>
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1816,11 +1732,11 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>185</v>
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1839,11 +1755,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>186</v>
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1859,11 +1775,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>187</v>
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1876,12 +1792,6 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1893,11 +1803,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>188</v>
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1910,14 +1820,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>189</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>48</v>
@@ -1930,7 +1834,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1938,8 +1842,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -1980,11 +1884,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>190</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2003,11 +1907,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>191</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2023,11 +1927,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>192</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2046,11 +1950,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>193</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2069,11 +1973,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>194</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2092,11 +1996,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>195</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2116,7 +2020,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -2124,8 +2028,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:J61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -2137,10 +2041,11 @@
     <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
     <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
     <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="10" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2168,13 +2073,16 @@
       <c r="I1" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>208</v>
+      <c r="J1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2189,12 +2097,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>209</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2212,12 +2120,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>210</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2235,12 +2143,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>211</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2258,12 +2166,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>212</v>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2281,12 +2189,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>213</v>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2301,12 +2209,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>214</v>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2324,12 +2232,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>215</v>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2347,12 +2255,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>216</v>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2370,12 +2278,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
-        <v>217</v>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2393,12 +2301,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>218</v>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2413,12 +2321,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>219</v>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2436,12 +2344,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>220</v>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2459,12 +2367,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>221</v>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2482,12 +2390,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>222</v>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2506,11 +2414,11 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>223</v>
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2522,18 +2430,18 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>224</v>
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2545,18 +2453,18 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>225</v>
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2568,15 +2476,15 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>226</v>
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2592,11 +2500,11 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>227</v>
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2608,18 +2516,18 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>228</v>
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2631,18 +2539,18 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>229</v>
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2654,15 +2562,15 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>230</v>
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2674,18 +2582,18 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>231</v>
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2697,7 +2605,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2707,11 +2615,11 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>232</v>
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2723,18 +2631,18 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>233</v>
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2746,15 +2654,15 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>234</v>
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2766,18 +2674,18 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>235</v>
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2796,11 +2704,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>236</v>
+      <c r="A30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2819,11 +2727,11 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>237</v>
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2839,11 +2747,11 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
-        <v>238</v>
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2859,11 +2767,11 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>239</v>
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2882,11 +2790,11 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>240</v>
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2905,11 +2813,11 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>241</v>
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2925,11 +2833,11 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>242</v>
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2948,11 +2856,11 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>243</v>
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2974,11 +2882,11 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
-        <v>244</v>
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2997,11 +2905,11 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
-        <v>245</v>
+      <c r="A39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -3017,11 +2925,11 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>246</v>
+      <c r="A40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -3040,11 +2948,11 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
-        <v>247</v>
+      <c r="A41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3063,11 +2971,11 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>248</v>
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3086,11 +2994,11 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
-        <v>249</v>
+      <c r="A43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3106,11 +3014,11 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>250</v>
+      <c r="A44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3126,11 +3034,11 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
-        <v>251</v>
+      <c r="A45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3149,11 +3057,11 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>252</v>
+      <c r="A46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3172,11 +3080,11 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
-        <v>253</v>
+      <c r="A47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3192,11 +3100,11 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" t="s">
-        <v>254</v>
+      <c r="A48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3214,12 +3122,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" t="s">
-        <v>255</v>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3240,12 +3148,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" t="s">
-        <v>256</v>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3263,12 +3171,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" t="s">
-        <v>257</v>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3283,12 +3191,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" t="s">
-        <v>258</v>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3306,12 +3214,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" t="s">
-        <v>259</v>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3323,18 +3231,12 @@
         <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" t="s">
-        <v>260</v>
-      </c>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3343,19 +3245,13 @@
         <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" t="s">
-        <v>54</v>
-      </c>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>36</v>
       </c>
@@ -3366,18 +3262,18 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>35</v>
-      </c>
-      <c r="B56" t="s">
-        <v>261</v>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3392,15 +3288,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" t="s">
-        <v>262</v>
-      </c>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3415,13 +3305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" t="s">
-        <v>55</v>
-      </c>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>36</v>
       </c>
@@ -3438,12 +3322,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>35</v>
-      </c>
-      <c r="B59" t="s">
-        <v>263</v>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3458,15 +3342,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>35</v>
-      </c>
-      <c r="B60" t="s">
-        <v>264</v>
-      </c>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3481,13 +3359,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" t="s">
-        <v>56</v>
-      </c>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>36</v>
       </c>
@@ -3504,8 +3376,77 @@
         <v>32</v>
       </c>
     </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3513,8 +3454,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -3612,7 +3553,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3620,8 +3561,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
@@ -3653,11 +3594,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>272</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3669,15 +3610,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>273</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3693,11 +3634,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>274</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3713,11 +3654,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3733,11 +3674,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>276</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3753,11 +3694,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>36</v>
@@ -3773,11 +3714,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
@@ -3793,11 +3734,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>36</v>
@@ -3813,13 +3754,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:G6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -3851,11 +3792,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>283</v>
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3867,15 +3808,15 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>284</v>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3891,11 +3832,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>285</v>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3911,11 +3852,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>286</v>
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3931,11 +3872,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>287</v>
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3951,13 +3892,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -3985,12 +3926,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>266</v>
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -4002,12 +3943,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>36</v>
@@ -4020,6 +3961,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C787E33F-805E-4CF6-80B4-CB20221C641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8900DF63-5559-41AD-9BE5-EB63803DC3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="7" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3877" yWindow="3143" windowWidth="21601" windowHeight="11325" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="163">
   <si>
     <t>Result</t>
   </si>
@@ -207,327 +207,18 @@
     <t>Mon Feb 24 23:39:49 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:42:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:42:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:42:58 EST 2025</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
     <t>June</t>
   </si>
   <si>
-    <t>Thu May 21 21:37:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:37:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:38:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:39:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 21:40:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:02:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:03:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:04:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:05:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:06:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:07:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:08:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:09:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:25:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:29:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:30:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:30:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:35:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri May 22 19:36:05 EDT 2026</t>
-  </si>
-  <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
     <t>MFInsNum</t>
   </si>
   <si>
-    <t>Thu Jul 09 17:34:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:34:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:34:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:35:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:35:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>Thu Jul 09 22:10:41 EDT 2026</t>
   </si>
   <si>
@@ -823,13 +514,30 @@
   </si>
   <si>
     <t>Thu Jul 09 22:22:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 18:59:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 18:59:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 19:00:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 15:30:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 15:30:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 15:30:51 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1202,15 +910,15 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1244,7 +952,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1256,7 +964,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>19</v>
@@ -1267,7 +975,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1279,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -1290,7 +998,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1302,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
@@ -1316,7 +1024,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1328,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1342,7 +1050,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1354,7 +1062,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1368,7 +1076,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1380,7 +1088,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>24</v>
@@ -1394,7 +1102,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1406,10 +1114,10 @@
         <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1427,14 +1135,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="13.0" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="13.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1468,7 +1176,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1485,7 +1193,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>169</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1502,7 +1210,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1519,7 +1227,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1539,7 +1247,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1559,7 +1267,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1579,7 +1287,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1599,7 +1307,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1619,7 +1327,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1639,7 +1347,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1659,7 +1367,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1679,7 +1387,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1699,7 +1407,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1719,7 +1427,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1736,7 +1444,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1759,7 +1467,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1779,7 +1487,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1807,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1846,15 +1554,15 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1888,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1911,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1931,7 +1639,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1954,7 +1662,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1977,7 +1685,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2000,7 +1708,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2032,17 +1740,17 @@
   <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.33203125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="39.53125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="39.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="11.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -2074,7 +1782,7 @@
         <v>49</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
@@ -2082,7 +1790,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2102,7 +1810,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2125,7 +1833,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2148,7 +1856,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2171,7 +1879,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2194,7 +1902,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2214,7 +1922,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2237,7 +1945,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2260,7 +1968,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2283,7 +1991,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2306,7 +2014,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2326,7 +2034,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2349,7 +2057,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2372,7 +2080,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2395,7 +2103,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2418,7 +2126,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2430,7 +2138,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -2441,7 +2149,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2453,7 +2161,7 @@
         <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>32</v>
@@ -2464,7 +2172,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>209</v>
+        <v>106</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2476,7 +2184,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
@@ -2484,7 +2192,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>210</v>
+        <v>107</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2504,7 +2212,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>211</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2516,7 +2224,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>32</v>
@@ -2527,7 +2235,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2539,7 +2247,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>32</v>
@@ -2550,7 +2258,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2562,7 +2270,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -2570,7 +2278,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2582,7 +2290,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>32</v>
@@ -2593,7 +2301,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2605,7 +2313,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -2619,7 +2327,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>216</v>
+        <v>113</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2631,7 +2339,7 @@
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>32</v>
@@ -2642,7 +2350,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2654,7 +2362,7 @@
         <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -2662,7 +2370,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2674,7 +2382,7 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>32</v>
@@ -2685,7 +2393,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2708,7 +2416,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2731,7 +2439,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2751,7 +2459,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>222</v>
+        <v>119</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2771,7 +2479,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2794,7 +2502,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2817,7 +2525,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2837,7 +2545,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2860,7 +2568,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2886,7 +2594,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2909,7 +2617,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2929,7 +2637,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2952,7 +2660,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -2975,7 +2683,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -2998,7 +2706,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3018,7 +2726,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3038,7 +2746,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3061,7 +2769,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3084,7 +2792,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3104,7 +2812,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3127,7 +2835,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3153,7 +2861,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3176,7 +2884,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3196,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3219,7 +2927,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3231,12 +2939,18 @@
         <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="C54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -3245,7 +2959,7 @@
         <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
@@ -3262,7 +2976,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
@@ -3273,7 +2987,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3289,8 +3003,14 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3327,7 +3047,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3343,8 +3063,14 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>16</v>
@@ -3381,7 +3107,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3390,10 +3116,10 @@
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>32</v>
@@ -3404,7 +3130,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3413,7 +3139,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>50</v>
@@ -3427,7 +3153,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>248</v>
+        <v>145</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3436,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>37</v>
@@ -3458,12 +3184,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3565,12 +3291,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3598,7 +3324,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3610,7 +3336,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3618,7 +3344,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3638,7 +3364,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3658,7 +3384,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3678,7 +3404,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3698,10 +3424,10 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
@@ -3710,7 +3436,7 @@
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -3718,10 +3444,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -3730,7 +3456,7 @@
         <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -3738,10 +3464,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -3750,7 +3476,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3763,12 +3489,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3796,7 +3522,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3808,7 +3534,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3816,7 +3542,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3836,7 +3562,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3856,7 +3582,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3876,7 +3602,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3901,12 +3627,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3931,7 +3657,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
